--- a/docs/FCC-core-55-70/launch-signoff-v1-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/launch-signoff-v1-2026-07-19.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1351,9 +1351,122 @@
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>First run · Step 1 — value intro</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Fresh install → the first screen (what MoneyKeel can do + the read-only promise)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Approved first-run flow; skippable</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>First run · Step 2 — the two questions</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>"What did you come for?" (pick all) + "Where are you these days?" (working / retired) — after the intro; also Settings → Your setup</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Sets the lens + tab order; answers only order suggestions</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>First run · retiree fast-path — Monthly income</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Answer "retired" + "a retirement paycheck" in step 2 → the 2-number Social Security / pension screen, no bank login</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>The retiree快 path; feeds the paycheck hero</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Full setup questionnaire (multi-step)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Settings → restart setup (or Sharpen → full setup) — walk every step: status, income, salary, spending, retirement…</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>The deep wizard; every step skippable with sensible defaults</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Home · first-run empty state (the doors)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Fresh account before any data — Home shows "Let's get your real numbers in" with Connect / Add by hand doors</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>No fake zeros; the two doors + what-you'll-see preview</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"READY FOR LAUNCH,FEEDBACK"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E42 E43 E44 E45 E46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"READY FOR LAUNCH,FEEDBACK"</formula1>
     </dataValidation>
   </dataValidations>
